--- a/tools/importer/reports/import-footer.report.xlsx
+++ b/tools/importer/reports/import-footer.report.xlsx
@@ -49,7 +49,7 @@
     <t>success</t>
   </si>
   <si>
-    <t>2026-06-11T16:34:14.904Z</t>
+    <t>2026-06-15T03:21:21.187Z</t>
   </si>
   <si>
     <t>Footer</t>
